--- a/outputs/50486.xlsx
+++ b/outputs/50486.xlsx
@@ -123,15 +123,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -345,7 +345,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="str">
-        <f aca="false">IF(ISNUMBER(C2),"Chep",IF(ISNUMBER(D2),"Loscam",""))</f>
+        <f aca="false">IF(ISNUMBER(C2),"Chep","Loscam")</f>
         <v>Chep</v>
       </c>
       <c r="B2" s="2"/>
@@ -356,7 +356,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="str">
-        <f aca="false">IF(ISNUMBER(C3),"Chep",IF(ISNUMBER(D3),"Loscam",""))</f>
+        <f aca="false">IF(ISNUMBER(C3),"Chep","Loscam")</f>
         <v>Chep</v>
       </c>
       <c r="B3" s="2"/>
@@ -367,7 +367,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="str">
-        <f aca="false">IF(ISNUMBER(C4),"Chep",IF(ISNUMBER(D4),"Loscam",""))</f>
+        <f aca="false">IF(ISNUMBER(C4),"Chep","Loscam")</f>
         <v>Loscam</v>
       </c>
       <c r="B4" s="2"/>
@@ -378,7 +378,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="str">
-        <f aca="false">IF(ISNUMBER(C5),"Chep",IF(ISNUMBER(D5),"Loscam",""))</f>
+        <f aca="false">IF(ISNUMBER(C5),"Chep","Loscam")</f>
         <v>Loscam</v>
       </c>
       <c r="B5" s="2"/>

--- a/outputs/50486.xlsx
+++ b/outputs/50486.xlsx
@@ -123,7 +123,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -331,7 +331,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="1" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -343,9 +343,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="str">
-        <f aca="false">IF(ISNUMBER(C2),"Chep","Loscam")</f>
+        <f aca="false">IF(AND(C2&lt;&gt;"",C2&lt;&gt;0),"Chep",IF(AND(D2&lt;&gt;"",D2&lt;&gt;0),"Loscam",""))</f>
         <v>Chep</v>
       </c>
       <c r="B2" s="2"/>
@@ -354,9 +354,9 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="str">
-        <f aca="false">IF(ISNUMBER(C3),"Chep","Loscam")</f>
+        <f aca="false">IF(AND(C3&lt;&gt;"",C3&lt;&gt;0),"Chep",IF(AND(D3&lt;&gt;"",D3&lt;&gt;0),"Loscam",""))</f>
         <v>Chep</v>
       </c>
       <c r="B3" s="2"/>
@@ -365,9 +365,9 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="str">
-        <f aca="false">IF(ISNUMBER(C4),"Chep","Loscam")</f>
+        <f aca="false">IF(AND(C4&lt;&gt;"",C4&lt;&gt;0),"Chep",IF(AND(D4&lt;&gt;"",D4&lt;&gt;0),"Loscam",""))</f>
         <v>Loscam</v>
       </c>
       <c r="B4" s="2"/>
@@ -376,9 +376,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="str">
-        <f aca="false">IF(ISNUMBER(C5),"Chep","Loscam")</f>
+        <f aca="false">IF(AND(C5&lt;&gt;"",C5&lt;&gt;0),"Chep",IF(AND(D5&lt;&gt;"",D5&lt;&gt;0),"Loscam",""))</f>
         <v>Loscam</v>
       </c>
       <c r="B5" s="2"/>
@@ -387,31 +387,31 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
